--- a/reports/OYPB_브랜드별_성과매트릭스_HAN_260908.xlsx
+++ b/reports/OYPB_브랜드별_성과매트릭스_HAN_260908.xlsx
@@ -573,7 +573,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:M20"/>
+  <dimension ref="A1:M22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="17" customWidth="1" min="1" max="1"/>
@@ -1350,11 +1350,11 @@
         <v/>
       </c>
       <c r="H16" s="20">
-        <f>ROUND(524201000/E16,1)</f>
+        <f>ROUND(900344264/E16,1)</f>
         <v/>
       </c>
       <c r="I16" s="19">
-        <f>ROUND(524201000/G16,0)</f>
+        <f>ROUND(900344264/G16,0)</f>
         <v/>
       </c>
       <c r="J16" s="18">
@@ -1385,24 +1385,40 @@
     <row r="19">
       <c r="A19" s="23" t="inlineStr">
         <is>
-          <t>※ 참여수 = 좋아요+댓글 · 평균 조회수 = 조회수÷성과 집계 건수 · 평균 CPV = 시딩 비용÷조회수 · 평균 CPE = 시딩 비용÷참여수 (시딩 비용 확인분 524,201,000원) · ROAS = 전환 매출÷광고비</t>
+          <t>※ 참여수 = 좋아요+댓글 · 평균 조회수 = 조회수÷성과 집계 건수 · ROAS = 전환 매출÷광고비</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="23" t="inlineStr">
         <is>
+          <t>※ 소계의 평균 CPV·CPE는 세금계산서 발행 총액 900,344,264원 기준 (2026.02~08 확정 840,514,264 + 2025 시딩 정산 59,830,000)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="23" t="inlineStr">
+        <is>
+          <t>※ 브랜드별 평균 CPV·CPE는 브랜드 귀속이 확인된 시딩 비용 524,201,000원 기준(국내는 원고료, 바이오힐보 해외는 청구액) — 발행 총액은 브랜드 귀속 미확정으로 안분하지 않음</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="23" t="inlineStr">
+        <is>
           <t>※ 좋아요 공란 519건은 추정하지 않음 → 참여수는 하한, 평균 CPE는 상한. 바이오힐보 (국내)·(해외) 행은 참고용이며 소계에 포함하지 않음</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="10">
     <mergeCell ref="A19:M19"/>
     <mergeCell ref="J1:L1"/>
     <mergeCell ref="B1:D1"/>
+    <mergeCell ref="A22:M22"/>
     <mergeCell ref="A18:M18"/>
     <mergeCell ref="E1:I1"/>
+    <mergeCell ref="A21:M21"/>
     <mergeCell ref="A20:M20"/>
     <mergeCell ref="M1:M2"/>
     <mergeCell ref="A1:A2"/>
